--- a/DATA/Processed/armax_master_dataframe.xlsx
+++ b/DATA/Processed/armax_master_dataframe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\GitHub\Masterthesis\DATA\Processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D985C16B-8879-47BB-9D61-FB8049A32049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C8C684-9EAE-4A0A-BDD0-3AB3C78425BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
